--- a/examples/zips/92258/92258_for_sale.xlsx
+++ b/examples/zips/92258/92258_for_sale.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:AR5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,106 @@
           <t>lot_sqft</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>lot_size_sqft</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>listing_description</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>hoa_fee</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>hoa_monthly_fee</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>raw_details</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>raw_tags</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>raw_photo_tags</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pool_available</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pool_type</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>is_private_pool</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>is_private_pool_known</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>private_pool_verified</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pool_conflict</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pool_community_only</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pool_confidence</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pool_signal_sources</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pool_evidence</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>has_pool_inferred</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>has_pool_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -596,7 +696,11 @@
           <t>Riverside</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Garnet Gardens</t>
+        </is>
+      </c>
       <c r="K2" t="n">
         <v>33.922143</v>
       </c>
@@ -617,7 +721,7 @@
         <v>1960</v>
       </c>
       <c r="R2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,10 +740,90 @@
         <v>55000</v>
       </c>
       <c r="W2" t="n">
-        <v>124</v>
+        <v>123.6024844720497</v>
       </c>
       <c r="X2" t="n">
         <v>8712</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8712</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Incredible investment Opportunity in this unique property with Two homes on a spacious 8,712 sq ft lot located in North Palm Springs. Complete with Beautiful views of the snow capped San Jacinto Mountains!! Since this is the First time this property has been on the market in 35 years, it offers an excellent potential for renovation and investment as a fix and flip project, live in one and rent the other, or create the perfect multi-generational environment. The main home has 2 bedrooms and 1 bath. Kitchen is open to the family room. 2nd exterior door provides quick access to the garage. The second home has 1 bedroom and 1 bath. Total square footage is 1,880 sq ft per assessor office and buyer to verify permits. Conveniently located one-car garage between the 2 homes. The workshop is the perfect area to transform it into a home office, children's play area, gym, game room, an outdoor lounge.... The possibilities are endless!! Newer cemented driveway. Relax and take in the mountain views under the vinyl courtyard patio. The side yard is a blank canvas for your creativity. There is damage to the ceiling in the second home and dried mud on the floor of the workshop. Just bring your tools and let the renovations begin!!</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Incredible investment Opportunity in this unique property with Two homes on a spacious 8,712 sq ft lot located in North Palm Springs. Complete with Beautiful views of the snow capped San Jacinto Mountains!! Since this is the First time this property has been on the market in 35 years, it offers an excellent potential for renovation and investment as a fix and flip project, live in one and rent the other, or create the perfect multi-generational environment. The main home has 2 bedrooms and 1 bath. Kitchen is open to the family room. 2nd exterior door provides quick access to the garage. The second home has 1 bedroom and 1 bath. Total square footage is 1,880 sq ft per assessor office and buyer to verify permits. Conveniently located one-car garage between the 2 homes. The workshop is the perfect area to transform it into a home office, children's play area, gym, game room, an outdoor lounge.... The possibilities are endless!! Newer cemented driveway. Relax and take in the mountain views under the vinyl courtyard patio. The side yard is a blank canvas for your creativity. There is damage to the ceiling in the second home and dried mud on the floor of the workshop. Just bring your tools and let the renovations begin!!</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[{"category": "Bedrooms", "text": ["Bedrooms: 3", "Bedrooms On Main Level: 3"], "parent_category": "Interior"}, {"category": "Bathrooms", "text": ["Total Bathrooms: 2", "Full Bathrooms: 2", "Bathrooms On Main Level: 2", "Bathroom 1 Features: Shower in Tub,Bathtub"], "parent_category": "Interior"}, {"category": "Appliances", "text": ["Refrigerator", "Free-Standing Range", "Laundry Features: Inside"], "parent_category": "Interior"}, {"category": "Other Rooms", "text": ["Workshop", "Kitchen", "Family Room"], "parent_category": "Interior"}, {"category": "Heating and Cooling", "text": ["Cooling Features: Wall/Window Unit(s)", "Heating Features: Central", "Heating: Yes"], "parent_category": "Interior"}, {"category": "Kitchen and Dining", "text": ["Breakfast Room Description: In Family Room", "Kitchen Features: Kitchen Open to Family Room"], "parent_category": "Interior"}, {"category": "Interior Features", "text": ["Flooring: Carpet, Laminate"], "parent_category": "Interior"}, {"category": "Land Info", "text": ["Additional Parcels: No", "Land Lease: No", "Lot Description: Lot 6500-9999, Front Yard, Back Yard", "Lot Size Acres: 0.2", "Lot Size Source: Assessor", "Lot Size Square Feet: 8712"], "parent_category": "Exterior"}, {"category": "Exterior and Lot Features", "text": ["Fencing: Chain Link", "Other Structures: Workshop, Two On A Lot", "Patio And Porch Features: Patio", "Road Frontage Type: City Street", "Patio: Yes"], "parent_category": "Exterior"}, {"category": "Garage and Parking", "text": ["Garage Spaces: 1", "Garage Description: 1", "Parking Features: Driveway", "Parking Total: 1"], "parent_category": "Exterior"}, {"category": "Home Features", "text": ["View: Mountain(s)"], "parent_category": "Exterior"}, {"category": "Homeowners Association", "text": ["Association: No", "Calculated Total Monthly Association Fees: 0"], "parent_category": "Community"}, {"category": "Multi-Unit Info", "text": ["Number of Units: 2"], "parent_category": "Community"}, {"category": "School Information", "text": ["School District: Palm Springs Unified"], "parent_category": "Community"}, {"category": "Rental Info", "text": ["Lease Considered: No"], "parent_category": "Community"}, {"category": "Amenities and Community Features", "text": ["Community Features: Rural"], "parent_category": "Community"}, {"category": "Other Property Info", "text": ["Source Listing Status: Active", "County: Riverside", "Directions: 10 fwy, 62 north, exit dillon Rd, right on Keith", "Source Property Type: Residential", "Inclusions: Stove and refrigerator", "Area: 699 - Not Defined", "Source Neighborhood: 699 - Not Defined", "Parcel Number: 666214005", "Property Subtype: Single Family Residence"], "parent_category": "Listing"}, {"category": "Building and Construction", "text": ["Total Square Feet Living: 1610.00", "Year Built: 1960", "Common Walls: No Common Walls", "Entry Level: 1", "Entry Location: patio courtyard", "Levels: One", "Living Area Source: Assessor", "Living Area Units: Square Feet", "Property Age: 66", "Property Attached: No", "Property Condition: Repairs Major, Fixer, Repairs Cosmetic", "Roof: Flat", "Levels or Stories: One", "Building Total Stories: 1", "Structure Type: House", "Elevation Units: Feet", "Year Built Source: Assessor"], "parent_category": "Features"}, {"category": "Utilities", "text": ["Sewer: Septic Type Unknown", "Water Source: Public"], "parent_category": "Features"}]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>["central_heat", "community_outdoor_space", "family_room", "hill_or_mountain_view", "laundry_room", "view", "single_story", "garage_1_or_more", "rental_property", "mountain_view", "investment_opportunity", "views", "playground", "home_office", "office", "game_room", "exercise_room", "patio", "fixer_upper"]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[{"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m3846321327s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m3435647156s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m2348238812s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m1053058417s.jpg", "labels": ["exterior", "exterior"]}]</t>
+        </is>
+      </c>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>community</t>
+        </is>
+      </c>
+      <c r="AI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>details,photo_tags,tags</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Garage Spaces: 1; community outdoor space</t>
+        </is>
+      </c>
+      <c r="AQ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>details,photo_tags,tags</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -688,7 +872,11 @@
           <t>Riverside</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Garnet Gardens</t>
+        </is>
+      </c>
       <c r="K3" t="n">
         <v>33.922687</v>
       </c>
@@ -709,7 +897,7 @@
         <v>1950</v>
       </c>
       <c r="R3" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -728,21 +916,97 @@
         <v>250000</v>
       </c>
       <c r="W3" t="n">
-        <v>480</v>
+        <v>479.9</v>
       </c>
       <c r="X3" t="n">
         <v>8712</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8712</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Turnkey Desert Charmer - Fully Remodeled &amp; STR-Ready! Welcome to this irresistibly cute desert retreat where modern design meets effortless comfort. Completely reimagined from the inside out, this home has undergone an extensive, no-expense-spared renovation-thoughtfully curated to feel fresh, stylish, and move-in ready for full-time living or a high-performing short-term rental. Every major system has been upgraded for peace of mind, including plumbing, electrical, gas, sewer, irrigation, and energy-efficient mini-split climate control. Brand-new windows bathe the interior in natural light, creating an airy, open feel throughout. The interiors are equal parts chic and cozy, featuring sleek concrete floors, a beautifully updated kitchen, and spa-inspired bathrooms with modern finishes. The primary bath steals the show with its custom polished concrete countertop-both striking and functional. Outside, the transformation continues. The home has new stucco for a clean, contemporary look and has been freshly painted inside and out. The backyard is an entertainer's dream with a stylish paver patio, brand-new Aluma wood patio cover with lighting and electrical, extensive artificial turf, new roof as of 2023, and a calming water feature that sets the tone for relaxed desert evenings. RV hookups add flexibility, while pre-run lines offer exciting potential for a future casita or expanded living space. Charming, turnkey, and packed with thoughtful upgrades, this desert oasis is perfectly suited as a primary residence, weekend getaway, or income-producing short-term rental. A rare blend of style, substance, and opportunity-this one is truly special.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Turnkey Desert Charmer - Fully Remodeled &amp; STR-Ready! Welcome to this irresistibly cute desert retreat where modern design meets effortless comfort. Completely reimagined from the inside out, this home has undergone an extensive, no-expense-spared renovation-thoughtfully curated to feel fresh, stylish, and move-in ready for full-time living or a high-performing short-term rental. Every major system has been upgraded for peace of mind, including plumbing, electrical, gas, sewer, irrigation, and energy-efficient mini-split climate control. Brand-new windows bathe the interior in natural light, creating an airy, open feel throughout. The interiors are equal parts chic and cozy, featuring sleek concrete floors, a beautifully updated kitchen, and spa-inspired bathrooms with modern finishes. The primary bath steals the show with its custom polished concrete countertop-both striking and functional. Outside, the transformation continues. The home has new stucco for a clean, contemporary look and has been freshly painted inside and out. The backyard is an entertainer's dream with a stylish paver patio, brand-new Aluma wood patio cover with lighting and electrical, extensive artificial turf, new roof as of 2023, and a calming water feature that sets the tone for relaxed desert evenings. RV hookups add flexibility, while pre-run lines offer exciting potential for a future casita or expanded living space. Charming, turnkey, and packed with thoughtful upgrades, this desert oasis is perfectly suited as a primary residence, weekend getaway, or income-producing short-term rental. A rare blend of style, substance, and opportunity-this one is truly special.</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[{"category": "Bedrooms", "text": ["Bedrooms: 2"], "parent_category": "Interior"}, {"category": "Bathrooms", "text": ["Total Bathrooms: 2", "Full Bathrooms: 2"], "parent_category": "Interior"}, {"category": "Appliances", "text": ["Laundry Features: Laundry Area"], "parent_category": "Interior"}, {"category": "Heating and Cooling", "text": ["Cooling Features: Air Conditioning", "Heating: Yes"], "parent_category": "Interior"}, {"category": "Interior Features", "text": ["Furnished Description: Unfurnished", "Flooring: Concrete"], "parent_category": "Interior"}, {"category": "Land Info", "text": ["Lot Size Acres: 0.2", "Lot Size Source: Assessor", "Lot Size Square Feet: 8712"], "parent_category": "Exterior"}, {"category": "Garage and Parking", "text": ["Parking Features: Driveway"], "parent_category": "Exterior"}, {"category": "Home Features", "text": ["View: Mountain(s)", "Security Features: Security System Leased"], "parent_category": "Exterior"}, {"category": "Homeowners Association", "text": ["Association: No", "Calculated Total Monthly Association Fees: 0"], "parent_category": "Community"}, {"category": "Other Property Info", "text": ["Standard", "Source Listing Status: Active", "County: Riverside", "Cross Street: Indian Canyon", "Source Property Type: Residential", "Area: 331 - Palm Springs North End", "Source Neighborhood: 331 - Palm Springs North End", "Parcel Number: 666213017", "Postal Code Plus 4: 449", "Property Subtype: Single Family Residence"], "parent_category": "Listing"}, {"category": "Building and Construction", "text": ["Total Square Feet Living: 1000", "Year Built: 1950", "Building Area Source: Assessor", "Building Area Total: 1000", "Levels: One", "Property Age: 76", "Levels or Stories: One", "Building Total Stories: 1", "Total Area Sqft: 1000"], "parent_category": "Features"}, {"category": "Utilities", "text": ["Sewer: Septic Tank"], "parent_category": "Features"}]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>["central_air", "community_security_features", "hill_or_mountain_view", "view", "single_story", "updated_kitchen", "rental_property", "efficient", "new_roof"]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[{"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3080564698s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3385898168s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3423489659s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m717155700s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m2166976519s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m598541128s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m2406550403s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior", "unknown"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m2309311555s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3398170202s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m326011019s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m2724393485s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m2409460022s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m1240291349s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3984998378s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m2266840452s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m2399171032s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m1289242502s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3178590047s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3420187395s.jpg", "labels": ["dining_room"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3388121907s.jpg", "labels": ["dining_room"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3819228893s.jpg", "labels": ["dining_room"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3836945905s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3120631351s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m1481932531s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m932956103s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m707351781s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3295764697s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3621293415s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3662831946s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3689138730s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m1238071677s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3681826479s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m345053022s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m916406650s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m384619025s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3910991367s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3682440338s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m2256669033s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m2658886204s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m841591803s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m465582417s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m2816296449s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m1736957166s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3638047464s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m4160998132s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m1233163122s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m53637410s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m32529035s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m3211560657s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m2900580117s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m1286640875s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m1990966483s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/85ca3f8519d7d3e0051b4bfe033b87e2l-m1060588235s.jpg", "labels": ["exterior", "exterior"]}]</t>
+        </is>
+      </c>
+      <c r="AG3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>community</t>
+        </is>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>details,photo_tags,tags</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>details,photo_tags,tags</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.realtor.com/realestateandhomes-detail/61612-Sagebrush-Rd_North-Palm-Springs_CA_92258_M10762-68959</t>
+          <t>https://www.realtor.com/realestateandhomes-detail/17102-Sanborn-St_North-Palm-Springs_CA_92258_M20175-81354</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1076268959</t>
+          <t>2017581354</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -757,7 +1021,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>61612 Sagebrush Rd</t>
+          <t>17102 Sanborn St</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -780,61 +1044,141 @@
           <t>Riverside</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Garnet Gardens</t>
+        </is>
+      </c>
       <c r="K4" t="n">
-        <v>33.929266</v>
+        <v>33.924152</v>
       </c>
       <c r="L4" t="n">
-        <v>-116.587339</v>
+        <v>-116.542756</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1985</v>
+        <v>1166</v>
       </c>
       <c r="Q4" t="n">
-        <v>1958</v>
+        <v>1972</v>
       </c>
       <c r="R4" t="n">
-        <v>264</v>
+        <v>116</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2025-08-02 01:22:52</t>
+          <t>2025-12-31 01:49:31</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2020-11-23 00:00:00</t>
+          <t>2024-04-15 00:00:00</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>550000</v>
+        <v>392000</v>
       </c>
       <c r="V4" t="n">
-        <v>343000</v>
+        <v>140000</v>
       </c>
       <c r="W4" t="n">
-        <v>277</v>
+        <v>336.1921097770154</v>
       </c>
       <c r="X4" t="n">
-        <v>217800</v>
+        <v>6534</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6534</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>DO NOT DISTURB TENANT. FOR ACCESS SEND OFFER SUBJECT TO INTERIOR INSPECTION NO EXCEPTIONS! Beautifully Updated Desert Retreat in North Palm Springs Tenant in Place Welcome to this bright and inviting 2 bedroom, 2 bath single family home offering 1,166 sqft of comfortable living on a generous 6,534 sqft lot. Thoughtfully maintained and move in ready, this property blends modern convenience with desert charm. Inside, enjoy an open living space filled with natural light, a spacious kitchen with ample cabinetry, and well appointed bedrooms offering privacy and comfort. The primary suite features its own bathroom, while the second bedroom and bath are perfect for guests, a home office, or additional flex space. Outside, the large lot provides endless possibilities create a desert garden, add outdoor living space, or simply enjoy the serene mountain views. Property will be sold with a good standing tenant in place. Ideal for investors seeking a stable, turnkey opportunity with immediate rental income. Property Highlights.</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>DO NOT DISTURB TENANT. FOR ACCESS SEND OFFER SUBJECT TO INTERIOR INSPECTION NO EXCEPTIONS! Beautifully Updated Desert Retreat in North Palm Springs Tenant in Place Welcome to this bright and inviting 2 bedroom, 2 bath single family home offering 1,166 sqft of comfortable living on a generous 6,534 sqft lot. Thoughtfully maintained and move in ready, this property blends modern convenience with desert charm. Inside, enjoy an open living space filled with natural light, a spacious kitchen with ample cabinetry, and well appointed bedrooms offering privacy and comfort. The primary suite features its own bathroom, while the second bedroom and bath are perfect for guests, a home office, or additional flex space. Outside, the large lot provides endless possibilities create a desert garden, add outdoor living space, or simply enjoy the serene mountain views. Property will be sold with a good standing tenant in place. Ideal for investors seeking a stable, turnkey opportunity with immediate rental income. Property Highlights.</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>[{"category": "Bedrooms", "text": ["Bedrooms: 3", "Bedrooms On Main Level: 2"], "parent_category": "Interior"}, {"category": "Bathrooms", "text": ["Total Bathrooms: 2", "Full Bathrooms: 2", "Bathrooms On Main Level: 2"], "parent_category": "Interior"}, {"category": "Other Rooms", "text": ["All Bedrooms Down"], "parent_category": "Interior"}, {"category": "Appliances", "text": ["Laundry Features: Outside"], "parent_category": "Interior"}, {"category": "Heating and Cooling", "text": ["Cooling Features: ENERGY STAR Qualified Equipment", "Fireplace Features: Living Room"], "parent_category": "Interior"}, {"category": "Land Info", "text": ["Additional Parcels: No", "Land Lease: No", "Lot Description: 0-1 Unit/Acre", "Lot Size Acres: 0.15", "Lot Size Source: Assessor", "Lot Size Square Feet: 6534"], "parent_category": "Exterior"}, {"category": "Home Features", "text": ["View: Desert"], "parent_category": "Exterior"}, {"category": "Homeowners Association", "text": ["Association: No", "Calculated Total Monthly Association Fees: 0"], "parent_category": "Community"}, {"category": "Multi-Unit Info", "text": ["Number of Units: 1"], "parent_category": "Community"}, {"category": "School Information", "text": ["School District: Palm Springs Unified"], "parent_category": "Community"}, {"category": "Rental Info", "text": ["Lease Considered: No"], "parent_category": "Community"}, {"category": "Amenities and Community Features", "text": ["Community Features: Rural"], "parent_category": "Community"}, {"category": "Other Property Info", "text": ["Source Listing Status: Active", "County: Riverside", "Directions: Dillon Rd to Sanborn St in North Palm Springs", "Source Property Type: Residential", "Area: 699 - Not Defined", "Source Neighborhood: 699 - Not Defined", "Parcel Number: 666203007", "Property Subtype: Single Family Residence"], "parent_category": "Listing"}, {"category": "Building and Construction", "text": ["Total Square Feet Living: 1166.00", "Year Built: 1972", "Common Walls: No Common Walls", "Entry Level: 1", "Entry Location: front", "Levels: One", "Living Area Source: Assessor", "Living Area Units: Square Feet", "Property Age: 54", "Property Attached: No", "Levels or Stories: One", "Building Total Stories: 1", "Structure Type: House", "Elevation Units: Feet", "Year Built Source: Public Records"], "parent_category": "Features"}, {"category": "Utilities", "text": ["Water Source: Public"], "parent_category": "Features"}]</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>["fireplace", "laundry_room", "view", "single_story", "modern_kitchen", "large_kitchen", "rental_property", "big_lot", "mountain_view", "views", "oversized_lot", "open_concept_living", "home_office", "office", "den"]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[{"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m1176109128s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m343232395s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m162869423s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m1448099605s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m3701902711s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m2543547282s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m2470907209s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m2362391289s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m994025944s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m3182648171s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m345522362s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m1394481995s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m3353316767s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m3558296843s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m261377310s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m3694103047s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m3929606085s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m853552883s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m3989948692s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m408769827s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m1031318691s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m2016362671s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m2006167109s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior", "exterior", "unknown"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m476432732s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m738051072s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m768247437s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m3815713696s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m3091295638s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/00044b975339371f96e0917dc084ee0fl-m3174011966s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior"]}]</t>
+        </is>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>details,photo_tags,tags</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>details,photo_tags,tags</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.realtor.com/realestateandhomes-detail/17102-Sanborn-St_North-Palm-Springs_CA_92258_M20175-81354</t>
+          <t>https://www.realtor.com/realestateandhomes-detail/61612-Sagebrush-Rd_North-Palm-Springs_CA_92258_M10762-68959</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2017581354</t>
+          <t>1076268959</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -849,7 +1193,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17102 Sanborn St</t>
+          <t>61612 Sagebrush Rd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -874,48 +1218,128 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>33.924152</v>
+        <v>33.929266</v>
       </c>
       <c r="L5" t="n">
-        <v>-116.542756</v>
+        <v>-116.587339</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1166</v>
+        <v>1985</v>
       </c>
       <c r="Q5" t="n">
-        <v>1972</v>
+        <v>1958</v>
       </c>
       <c r="R5" t="n">
-        <v>113</v>
+        <v>267</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2025-12-31 01:49:31</t>
+          <t>2025-08-02 01:22:52</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2024-04-15 00:00:00</t>
+          <t>2020-11-23 00:00:00</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>349000</v>
+        <v>550000</v>
       </c>
       <c r="V5" t="n">
-        <v>140000</v>
+        <v>343000</v>
       </c>
       <c r="W5" t="n">
-        <v>299</v>
+        <v>277.0780856423174</v>
       </c>
       <c r="X5" t="n">
-        <v>6534</v>
+        <v>217800</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>217800</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Enjoy the desert tranquility and breathtaking views of San Jacinto from your own private gateway. This unique 4 bedrooms, 2 bath home on a huge 5 acres lot, offers the perfect blend of comfort and convenience. Thoughtfully designed for the perfect escape from the city, this home offers stunning sunsets with mountain views, easy access to outdoor adventure and a sleek, low-maintenance lifestyle. Whether you looking for a weekend retreat or an Airbnb income generator smart investment, this home delivers style, comfort, and convenience. There are so many opportunities offered by this property and its extensive 5 acres of land. For the savvy investor, the Airbnb permits are still available in this neighborhood. Interested in an assumable loan in this high interest rate environment? Seller has an FHA assumable loan at an incredible low rate (subject to seller's current lender approval). Desert Hills Premium Outlets is only 15 minutes away and downtown Palm Springs is 20 minutes away.</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Enjoy the desert tranquility and breathtaking views of San Jacinto from your own private gateway. This unique 4 bedrooms, 2 bath home on a huge 5 acres lot, offers the perfect blend of comfort and convenience. Thoughtfully designed for the perfect escape from the city, this home offers stunning sunsets with mountain views, easy access to outdoor adventure and a sleek, low-maintenance lifestyle. Whether you looking for a weekend retreat or an Airbnb income generator smart investment, this home delivers style, comfort, and convenience. There are so many opportunities offered by this property and its extensive 5 acres of land. For the savvy investor, the Airbnb permits are still available in this neighborhood. Interested in an assumable loan in this high interest rate environment? Seller has an FHA assumable loan at an incredible low rate (subject to seller's current lender approval). Desert Hills Premium Outlets is only 15 minutes away and downtown Palm Springs is 20 minutes away.</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>[{"category": "Bedrooms", "text": ["Bedrooms: 4", "Bedrooms On Main Level: 4"], "parent_category": "Interior"}, {"category": "Bathrooms", "text": ["Total Bathrooms: 2", "Full Bathrooms: 2", "Bathrooms On Main Level: 2"], "parent_category": "Interior"}, {"category": "Other Rooms", "text": ["All Bedrooms Down"], "parent_category": "Interior"}, {"category": "Appliances", "text": ["Laundry Features: Inside"], "parent_category": "Interior"}, {"category": "Heating and Cooling", "text": ["Cooling Features: Central Air", "Fireplace Features: Living Room", "Heating Features: Central", "Heating: Yes"], "parent_category": "Interior"}, {"category": "Kitchen and Dining", "text": ["Breakfast Room Description: In Kitchen"], "parent_category": "Interior"}, {"category": "Land Info", "text": ["Additional Parcels: No", "Land Lease: No", "Lot Description: 2-5 Units/Acre", "Lot Size Acres: 5.0", "Lot Size Source: Assessor", "Lot Size Square Feet: 217800"], "parent_category": "Exterior"}, {"category": "Exterior and Lot Features", "text": ["Road Surface Type: Unpaved"], "parent_category": "Exterior"}, {"category": "Garage and Parking", "text": ["Parking Features: Carport"], "parent_category": "Exterior"}, {"category": "Home Features", "text": ["View: Desert, Mountain(s)"], "parent_category": "Exterior"}, {"category": "Homeowners Association", "text": ["Association: No", "Calculated Total Monthly Association Fees: 0"], "parent_category": "Community"}, {"category": "Multi-Unit Info", "text": ["Number of Units: 1"], "parent_category": "Community"}, {"category": "School Information", "text": ["School District: Palm Springs Unified"], "parent_category": "Community"}, {"category": "Rental Info", "text": ["Lease Considered: No"], "parent_category": "Community"}, {"category": "Amenities and Community Features", "text": ["Community Features: Hiking, Mountainous, Rural"], "parent_category": "Community"}, {"category": "Other Property Info", "text": ["Source Listing Status: Active", "County: Riverside", "Directions: Indian Canyon Dr to Dillon Rd, right on Valley View Dr, right on Sagebrush Rd (2nd street).", "Source Property Type: Residential", "Area: 699 - Not Defined", "Source Neighborhood: 699 - Not Defined", "Parcel Number: 668220014", "Postal Code Plus 4: 0496", "Zoning: W-2", "Property Subtype: Single Family Residence"], "parent_category": "Listing"}, {"category": "Building and Construction", "text": ["Total Square Feet Living: 1985.00", "Year Built: 1958", "Common Walls: No Common Walls", "Entry Level: 1", "Entry Location: main", "Levels: One", "Living Area Source: Assessor", "Living Area Units: Square Feet", "Property Age: 68", "Property Attached: No", "Property Condition: Turnkey", "Levels or Stories: One", "Building Total Stories: 1", "Structure Type: House", "Elevation Units: Feet", "Year Built Source: Assessor", "Architectural Style: Ranch"], "parent_category": "Features"}, {"category": "Utilities", "text": ["Sewer: Septic Type Unknown", "Water Source: Public"], "parent_category": "Features"}]</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>["carport", "central_air", "central_heat", "fireplace", "hill_or_mountain_view", "laundry_room", "view", "single_story", "rental_property", "big_lot", "mountain_view", "breathtaking_views", "views"]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[{"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3200075157s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1664683402s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m46284255s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1575544242s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1372693044s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2065356000s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2622041543s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2916504500s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1923579425s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2504931907s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2014307786s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m781359343s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m267476246s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1464024972s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1534993186s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2629666874s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3073786309s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m703726341s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1126583630s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m722501013s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2508561337s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2589039701s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m172142027s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3296881792s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m562999200s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m4170372171s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1410007878s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2981440721s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1983704122s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m224018912s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3639343553s.jpg", "labels": ["exterior", "exterior", "exterior", "swimming_pool"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2637726737s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3581863079s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3098624546s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3621514268s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1553673971s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1693713241s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3787841785s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m4249936533s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m291358948s.jpg", "labels": ["exterior"]}]</t>
+        </is>
+      </c>
+      <c r="AG5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>details,photo_tags,tags</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>swimming pool</t>
+        </is>
+      </c>
+      <c r="AQ5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>details,photo_tags,tags</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/examples/zips/92258/92258_for_sale.xlsx
+++ b/examples/zips/92258/92258_for_sale.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR5"/>
+  <dimension ref="A1:AR4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,7 +721,7 @@
         <v>1960</v>
       </c>
       <c r="R2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -750,12 +750,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Incredible investment Opportunity in this unique property with Two homes on a spacious 8,712 sq ft lot located in North Palm Springs. Complete with Beautiful views of the snow capped San Jacinto Mountains!! Since this is the First time this property has been on the market in 35 years, it offers an excellent potential for renovation and investment as a fix and flip project, live in one and rent the other, or create the perfect multi-generational environment. The main home has 2 bedrooms and 1 bath. Kitchen is open to the family room. 2nd exterior door provides quick access to the garage. The second home has 1 bedroom and 1 bath. Total square footage is 1,880 sq ft per assessor office and buyer to verify permits. Conveniently located one-car garage between the 2 homes. The workshop is the perfect area to transform it into a home office, children's play area, gym, game room, an outdoor lounge.... The possibilities are endless!! Newer cemented driveway. Relax and take in the mountain views under the vinyl courtyard patio. The side yard is a blank canvas for your creativity. There is damage to the ceiling in the second home and dried mud on the floor of the workshop. Just bring your tools and let the renovations begin!!</t>
+          <t>Incredible investment Opportunity in this unique property with Two homes on a spacious 8,712 sq ft lot located in North Palm Springs. Complete with Beautiful views of the San Jacinto Mountains!! Since this is the First time this property has been on the market in 35 years, it offers an excellent potential for renovation and investment as a fix and flip project, live in one and rent the other, or create the perfect multi-generational environment. The main home has 2 bedrooms and 1 bath. Kitchen is open to the family room. 2nd exterior door provides quick access to the garage. The second home has 1 bedroom and 1 bath. Total square footage is 1,880 sq ft per assessor office and buyer to verify permits. Conveniently located one-car garage between the 2 homes. Each home has its own electric meter and water heater. The workshop is the perfect area to transform it into a home office, children's play area, gym, game room, an outdoor lounge.... The possibilities are endless!! Newer cemented driveway. Relax and take in the mountain views under the shady vinyl courtyard patio. The side yard is a blank canvas for your creativity. There is damage to one area of the ceiling in the second home and dried mud on the floor of the workshop. Just bring your tools and let the renovations begin!!</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Incredible investment Opportunity in this unique property with Two homes on a spacious 8,712 sq ft lot located in North Palm Springs. Complete with Beautiful views of the snow capped San Jacinto Mountains!! Since this is the First time this property has been on the market in 35 years, it offers an excellent potential for renovation and investment as a fix and flip project, live in one and rent the other, or create the perfect multi-generational environment. The main home has 2 bedrooms and 1 bath. Kitchen is open to the family room. 2nd exterior door provides quick access to the garage. The second home has 1 bedroom and 1 bath. Total square footage is 1,880 sq ft per assessor office and buyer to verify permits. Conveniently located one-car garage between the 2 homes. The workshop is the perfect area to transform it into a home office, children's play area, gym, game room, an outdoor lounge.... The possibilities are endless!! Newer cemented driveway. Relax and take in the mountain views under the vinyl courtyard patio. The side yard is a blank canvas for your creativity. There is damage to the ceiling in the second home and dried mud on the floor of the workshop. Just bring your tools and let the renovations begin!!</t>
+          <t>Incredible investment Opportunity in this unique property with Two homes on a spacious 8,712 sq ft lot located in North Palm Springs. Complete with Beautiful views of the San Jacinto Mountains!! Since this is the First time this property has been on the market in 35 years, it offers an excellent potential for renovation and investment as a fix and flip project, live in one and rent the other, or create the perfect multi-generational environment. The main home has 2 bedrooms and 1 bath. Kitchen is open to the family room. 2nd exterior door provides quick access to the garage. The second home has 1 bedroom and 1 bath. Total square footage is 1,880 sq ft per assessor office and buyer to verify permits. Conveniently located one-car garage between the 2 homes. Each home has its own electric meter and water heater. The workshop is the perfect area to transform it into a home office, children's play area, gym, game room, an outdoor lounge.... The possibilities are endless!! Newer cemented driveway. Relax and take in the mountain views under the shady vinyl courtyard patio. The side yard is a blank canvas for your creativity. There is damage to one area of the ceiling in the second home and dried mud on the floor of the workshop. Just bring your tools and let the renovations begin!!</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[{"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m3846321327s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m3435647156s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m2348238812s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m1053058417s.jpg", "labels": ["exterior", "exterior"]}]</t>
+          <t>[{"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m1491716075s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m826847626s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m2282386473s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m709621985s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m2341698334s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m3726687476s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m179962357s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m2553722161s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m3168336684s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m2838721217s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m1008714397s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m1440061965s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/b93b02e1982139086b6613d76e15462fl-m3571219395s.jpg", "labels": ["unknown"]}]</t>
         </is>
       </c>
       <c r="AG2" t="b">
@@ -897,7 +897,7 @@
         <v>1950</v>
       </c>
       <c r="R3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>1972</v>
       </c>
       <c r="R4" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1165,178 +1165,6 @@
         <v>0</v>
       </c>
       <c r="AR4" t="inlineStr">
-        <is>
-          <t>details,photo_tags,tags</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.realtor.com/realestateandhomes-detail/61612-Sagebrush-Rd_North-Palm-Springs_CA_92258_M10762-68959</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1076268959</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SINGLE_FAMILY</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>FOR_SALE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>61612 Sagebrush Rd</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>North Palm Springs</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>92258</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>33.929266</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-116.587339</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1958</v>
-      </c>
-      <c r="R5" t="n">
-        <v>267</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2025-08-02 01:22:52</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2020-11-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>550000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>343000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>277.0780856423174</v>
-      </c>
-      <c r="X5" t="n">
-        <v>217800</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>217800</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Enjoy the desert tranquility and breathtaking views of San Jacinto from your own private gateway. This unique 4 bedrooms, 2 bath home on a huge 5 acres lot, offers the perfect blend of comfort and convenience. Thoughtfully designed for the perfect escape from the city, this home offers stunning sunsets with mountain views, easy access to outdoor adventure and a sleek, low-maintenance lifestyle. Whether you looking for a weekend retreat or an Airbnb income generator smart investment, this home delivers style, comfort, and convenience. There are so many opportunities offered by this property and its extensive 5 acres of land. For the savvy investor, the Airbnb permits are still available in this neighborhood. Interested in an assumable loan in this high interest rate environment? Seller has an FHA assumable loan at an incredible low rate (subject to seller's current lender approval). Desert Hills Premium Outlets is only 15 minutes away and downtown Palm Springs is 20 minutes away.</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Enjoy the desert tranquility and breathtaking views of San Jacinto from your own private gateway. This unique 4 bedrooms, 2 bath home on a huge 5 acres lot, offers the perfect blend of comfort and convenience. Thoughtfully designed for the perfect escape from the city, this home offers stunning sunsets with mountain views, easy access to outdoor adventure and a sleek, low-maintenance lifestyle. Whether you looking for a weekend retreat or an Airbnb income generator smart investment, this home delivers style, comfort, and convenience. There are so many opportunities offered by this property and its extensive 5 acres of land. For the savvy investor, the Airbnb permits are still available in this neighborhood. Interested in an assumable loan in this high interest rate environment? Seller has an FHA assumable loan at an incredible low rate (subject to seller's current lender approval). Desert Hills Premium Outlets is only 15 minutes away and downtown Palm Springs is 20 minutes away.</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>[{"category": "Bedrooms", "text": ["Bedrooms: 4", "Bedrooms On Main Level: 4"], "parent_category": "Interior"}, {"category": "Bathrooms", "text": ["Total Bathrooms: 2", "Full Bathrooms: 2", "Bathrooms On Main Level: 2"], "parent_category": "Interior"}, {"category": "Other Rooms", "text": ["All Bedrooms Down"], "parent_category": "Interior"}, {"category": "Appliances", "text": ["Laundry Features: Inside"], "parent_category": "Interior"}, {"category": "Heating and Cooling", "text": ["Cooling Features: Central Air", "Fireplace Features: Living Room", "Heating Features: Central", "Heating: Yes"], "parent_category": "Interior"}, {"category": "Kitchen and Dining", "text": ["Breakfast Room Description: In Kitchen"], "parent_category": "Interior"}, {"category": "Land Info", "text": ["Additional Parcels: No", "Land Lease: No", "Lot Description: 2-5 Units/Acre", "Lot Size Acres: 5.0", "Lot Size Source: Assessor", "Lot Size Square Feet: 217800"], "parent_category": "Exterior"}, {"category": "Exterior and Lot Features", "text": ["Road Surface Type: Unpaved"], "parent_category": "Exterior"}, {"category": "Garage and Parking", "text": ["Parking Features: Carport"], "parent_category": "Exterior"}, {"category": "Home Features", "text": ["View: Desert, Mountain(s)"], "parent_category": "Exterior"}, {"category": "Homeowners Association", "text": ["Association: No", "Calculated Total Monthly Association Fees: 0"], "parent_category": "Community"}, {"category": "Multi-Unit Info", "text": ["Number of Units: 1"], "parent_category": "Community"}, {"category": "School Information", "text": ["School District: Palm Springs Unified"], "parent_category": "Community"}, {"category": "Rental Info", "text": ["Lease Considered: No"], "parent_category": "Community"}, {"category": "Amenities and Community Features", "text": ["Community Features: Hiking, Mountainous, Rural"], "parent_category": "Community"}, {"category": "Other Property Info", "text": ["Source Listing Status: Active", "County: Riverside", "Directions: Indian Canyon Dr to Dillon Rd, right on Valley View Dr, right on Sagebrush Rd (2nd street).", "Source Property Type: Residential", "Area: 699 - Not Defined", "Source Neighborhood: 699 - Not Defined", "Parcel Number: 668220014", "Postal Code Plus 4: 0496", "Zoning: W-2", "Property Subtype: Single Family Residence"], "parent_category": "Listing"}, {"category": "Building and Construction", "text": ["Total Square Feet Living: 1985.00", "Year Built: 1958", "Common Walls: No Common Walls", "Entry Level: 1", "Entry Location: main", "Levels: One", "Living Area Source: Assessor", "Living Area Units: Square Feet", "Property Age: 68", "Property Attached: No", "Property Condition: Turnkey", "Levels or Stories: One", "Building Total Stories: 1", "Structure Type: House", "Elevation Units: Feet", "Year Built Source: Assessor", "Architectural Style: Ranch"], "parent_category": "Features"}, {"category": "Utilities", "text": ["Sewer: Septic Type Unknown", "Water Source: Public"], "parent_category": "Features"}]</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>["carport", "central_air", "central_heat", "fireplace", "hill_or_mountain_view", "laundry_room", "view", "single_story", "rental_property", "big_lot", "mountain_view", "breathtaking_views", "views"]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[{"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3200075157s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1664683402s.jpg", "labels": ["exterior", "exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m46284255s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1575544242s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1372693044s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2065356000s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2622041543s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2916504500s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1923579425s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2504931907s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2014307786s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m781359343s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m267476246s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1464024972s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1534993186s.jpg", "labels": ["kitchen"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2629666874s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3073786309s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m703726341s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1126583630s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m722501013s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2508561337s.jpg", "labels": ["bedroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2589039701s.jpg", "labels": ["unknown"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m172142027s.jpg", "labels": ["living_room"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3296881792s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m562999200s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m4170372171s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1410007878s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2981440721s.jpg", "labels": ["bathroom"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1983704122s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m224018912s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3639343553s.jpg", "labels": ["exterior", "exterior", "exterior", "swimming_pool"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m2637726737s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3581863079s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3098624546s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3621514268s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1553673971s.jpg", "labels": ["exterior", "exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m1693713241s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m3787841785s.jpg", "labels": ["exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m4249936533s.jpg", "labels": ["exterior", "exterior"]}, {"href": "https://ap.rdcpix.com/42f13f44dc366a51b18f9200aa2a88eel-m291358948s.jpg", "labels": ["exterior"]}]</t>
-        </is>
-      </c>
-      <c r="AG5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AI5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>details,photo_tags,tags</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>swimming pool</t>
-        </is>
-      </c>
-      <c r="AQ5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="inlineStr">
         <is>
           <t>details,photo_tags,tags</t>
         </is>
